--- a/docs/samples/fob/03-freight-bill.xlsx
+++ b/docs/samples/fob/03-freight-bill.xlsx
@@ -462,19 +462,19 @@
         <v/>
       </c>
       <c r="M6" t="str">
-        <v>海运费(USD)</v>
+        <v>海运费(CNY)</v>
       </c>
       <c r="N6" t="str">
         <v/>
       </c>
       <c r="O6" t="str">
-        <v>文件费(USD)</v>
+        <v>文件费(CNY)</v>
       </c>
       <c r="P6" t="str">
         <v/>
       </c>
       <c r="Q6" t="str">
-        <v>VGM(USD)</v>
+        <v>VGM(CNY)</v>
       </c>
       <c r="R6" t="str">
         <v/>
